--- a/Projektplanung_Rechteck.xlsx
+++ b/Projektplanung_Rechteck.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahk\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95862B2-82D6-4305-AEE8-D8A54E3914F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4B67A1-7A34-462B-AF4E-210A0472FE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="54">
   <si>
     <t>Projektname:</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>Fertig</t>
+  </si>
+  <si>
+    <t>Saif</t>
   </si>
 </sst>
 </file>
@@ -658,9 +661,11 @@
       <c r="C9" s="4">
         <v>5</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="E9" s="4" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -673,9 +678,11 @@
       <c r="C10" s="3">
         <v>60</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="E10" s="3" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -688,9 +695,11 @@
       <c r="C11" s="4">
         <v>20</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="E11" s="4" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -703,9 +712,11 @@
       <c r="C12" s="4">
         <v>15</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="E12" s="4" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -718,9 +729,11 @@
       <c r="C13" s="4">
         <v>15</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="E13" s="4" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -733,7 +746,9 @@
       <c r="C14" s="4">
         <v>10</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="E14" s="4" t="s">
         <v>52</v>
       </c>
@@ -750,7 +765,7 @@
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -780,9 +795,11 @@
       <c r="C17" s="4">
         <v>15</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="E17" s="4" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -795,9 +812,11 @@
       <c r="C18" s="4">
         <v>15</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="E18" s="4" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -810,9 +829,11 @@
       <c r="C19" s="4">
         <v>20</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="E19" s="4" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -825,9 +846,11 @@
       <c r="C20" s="4">
         <v>25</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="E20" s="4" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -842,7 +865,7 @@
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -855,9 +878,11 @@
       <c r="C22" s="4">
         <v>30</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="E22" s="4" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -870,9 +895,11 @@
       <c r="C23" s="4">
         <v>20</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="E23" s="4" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -885,9 +912,11 @@
       <c r="C24" s="4">
         <v>10</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="E24" s="4" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
